--- a/Data/EXCEL/Transfer/dividend/20260225_0_4/5283-dividend-20260225_0_4.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260225_0_4/5283-dividend-20260225_0_4.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260225_0_4\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\20260225_0_4\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{BFA61CC7-CFAB-4A9A-9595-356D97EF99E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{657E246D-5546-4405-87B8-A3A390B44A64}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4140" yWindow="576" windowWidth="16656" windowHeight="10992" xr2:uid="{A4636D48-A0A9-4633-9414-CA53686FDB15}"/>
+    <workbookView xWindow="780" yWindow="780" windowWidth="22845" windowHeight="19530" xr2:uid="{D400D8CF-DD2C-441C-939A-6B7C2F1C4664}"/>
   </bookViews>
   <sheets>
     <sheet name="5283-dividend-20260225_0_4" sheetId="2" r:id="rId1"/>
@@ -1543,25 +1543,25 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{430D7617-A317-4E6D-B486-4CF7613C4209}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9FC9254F-6178-4273-837A-7443F052AE11}">
   <dimension ref="A1:R34"/>
-  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="5.109375" customWidth="1"/>
-    <col min="2" max="2" width="8.77734375" customWidth="1"/>
-    <col min="3" max="3" width="8.6640625" customWidth="1"/>
-    <col min="4" max="4" width="8.33203125" customWidth="1"/>
-    <col min="5" max="5" width="8" customWidth="1"/>
-    <col min="6" max="6" width="8.33203125" customWidth="1"/>
-    <col min="7" max="9" width="8" customWidth="1"/>
-    <col min="10" max="10" width="8.33203125" customWidth="1"/>
-    <col min="11" max="13" width="8" customWidth="1"/>
-    <col min="14" max="14" width="8.33203125" customWidth="1"/>
-    <col min="15" max="17" width="8" customWidth="1"/>
-    <col min="18" max="18" width="8.44140625" customWidth="1"/>
+    <col min="1" max="1" width="6.375" customWidth="1"/>
+    <col min="2" max="2" width="10.875" customWidth="1"/>
+    <col min="3" max="3" width="10.625" customWidth="1"/>
+    <col min="4" max="4" width="10.375" customWidth="1"/>
+    <col min="5" max="5" width="9.875" customWidth="1"/>
+    <col min="6" max="6" width="10.375" customWidth="1"/>
+    <col min="7" max="9" width="9.875" customWidth="1"/>
+    <col min="10" max="10" width="10.375" customWidth="1"/>
+    <col min="11" max="13" width="9.875" customWidth="1"/>
+    <col min="14" max="14" width="10.375" customWidth="1"/>
+    <col min="15" max="17" width="9.875" customWidth="1"/>
+    <col min="18" max="18" width="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:18" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A1" s="23" t="s">
         <v>0</v>
       </c>
@@ -1589,7 +1589,7 @@
       <c r="Q1" s="32"/>
       <c r="R1" s="24"/>
     </row>
-    <row r="2" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A2" s="25" t="s">
         <v>1</v>
       </c>
@@ -1619,7 +1619,7 @@
       <c r="Q2" s="34"/>
       <c r="R2" s="35"/>
     </row>
-    <row r="3" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A3" s="25" t="s">
         <v>2</v>
       </c>
@@ -1665,7 +1665,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A4" s="27"/>
       <c r="B4" s="28"/>
       <c r="C4" s="7"/>
@@ -1715,7 +1715,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="5" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A5" s="39">
         <v>2026</v>
       </c>
@@ -1769,7 +1769,7 @@
         <v>3.32</v>
       </c>
     </row>
-    <row r="6" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A6" s="41"/>
       <c r="B6" s="42"/>
       <c r="C6" s="44"/>
@@ -1795,7 +1795,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="7" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
         <v>27</v>
       </c>
@@ -1851,7 +1851,7 @@
         <v>1.66</v>
       </c>
     </row>
-    <row r="8" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A8" s="49">
         <v>2025</v>
       </c>
@@ -1905,7 +1905,7 @@
         <v>3.38</v>
       </c>
     </row>
-    <row r="9" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A9" s="19" t="s">
         <v>27</v>
       </c>
@@ -1961,7 +1961,7 @@
         <v>2.0299999999999998</v>
       </c>
     </row>
-    <row r="10" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A10" s="19" t="s">
         <v>27</v>
       </c>
@@ -2017,7 +2017,7 @@
         <v>1.35</v>
       </c>
     </row>
-    <row r="11" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A11" s="51">
         <v>2024</v>
       </c>
@@ -2071,7 +2071,7 @@
         <v>7.11</v>
       </c>
     </row>
-    <row r="12" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A12" s="11" t="s">
         <v>27</v>
       </c>
@@ -2127,7 +2127,7 @@
         <v>3.69</v>
       </c>
     </row>
-    <row r="13" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A13" s="11" t="s">
         <v>27</v>
       </c>
@@ -2183,7 +2183,7 @@
         <v>3.42</v>
       </c>
     </row>
-    <row r="14" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A14" s="49">
         <v>2023</v>
       </c>
@@ -2237,7 +2237,7 @@
         <v>7.06</v>
       </c>
     </row>
-    <row r="15" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A15" s="19" t="s">
         <v>27</v>
       </c>
@@ -2293,7 +2293,7 @@
         <v>3.49</v>
       </c>
     </row>
-    <row r="16" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A16" s="19" t="s">
         <v>27</v>
       </c>
@@ -2349,7 +2349,7 @@
         <v>3.57</v>
       </c>
     </row>
-    <row r="17" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A17" s="51">
         <v>2022</v>
       </c>
@@ -2403,7 +2403,7 @@
         <v>6.9</v>
       </c>
     </row>
-    <row r="18" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A18" s="11" t="s">
         <v>27</v>
       </c>
@@ -2459,7 +2459,7 @@
         <v>3.57</v>
       </c>
     </row>
-    <row r="19" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A19" s="11" t="s">
         <v>27</v>
       </c>
@@ -2515,7 +2515,7 @@
         <v>3.33</v>
       </c>
     </row>
-    <row r="20" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A20" s="49">
         <v>2021</v>
       </c>
@@ -2569,7 +2569,7 @@
         <v>6.24</v>
       </c>
     </row>
-    <row r="21" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A21" s="19" t="s">
         <v>27</v>
       </c>
@@ -2625,7 +2625,7 @@
         <v>3.38</v>
       </c>
     </row>
-    <row r="22" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A22" s="19" t="s">
         <v>27</v>
       </c>
@@ -2681,7 +2681,7 @@
         <v>2.87</v>
       </c>
     </row>
-    <row r="23" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A23" s="51">
         <v>2020</v>
       </c>
@@ -2735,7 +2735,7 @@
         <v>8.7100000000000009</v>
       </c>
     </row>
-    <row r="24" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A24" s="11" t="s">
         <v>27</v>
       </c>
@@ -2791,7 +2791,7 @@
         <v>3.84</v>
       </c>
     </row>
-    <row r="25" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A25" s="11" t="s">
         <v>27</v>
       </c>
@@ -2847,7 +2847,7 @@
         <v>4.87</v>
       </c>
     </row>
-    <row r="26" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A26" s="49">
         <v>2019</v>
       </c>
@@ -2901,7 +2901,7 @@
         <v>8.4499999999999993</v>
       </c>
     </row>
-    <row r="27" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A27" s="51">
         <v>2018</v>
       </c>
@@ -2955,7 +2955,7 @@
         <v>6.17</v>
       </c>
     </row>
-    <row r="28" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A28" s="49">
         <v>2017</v>
       </c>
@@ -3009,7 +3009,7 @@
         <v>3.32</v>
       </c>
     </row>
-    <row r="29" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A29" s="51">
         <v>2016</v>
       </c>
@@ -3063,7 +3063,7 @@
         <v>2.0699999999999998</v>
       </c>
     </row>
-    <row r="30" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A30" s="49">
         <v>2015</v>
       </c>
@@ -3117,7 +3117,7 @@
         <v>4.55</v>
       </c>
     </row>
-    <row r="31" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A31" s="51">
         <v>2014</v>
       </c>
@@ -3171,7 +3171,7 @@
         <v>4.76</v>
       </c>
     </row>
-    <row r="32" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A32" s="49">
         <v>2013</v>
       </c>
@@ -3225,7 +3225,7 @@
         <v>2.56</v>
       </c>
     </row>
-    <row r="33" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A33" s="51">
         <v>2012</v>
       </c>
@@ -3279,7 +3279,7 @@
         <v>3.67</v>
       </c>
     </row>
-    <row r="34" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A34" s="49" t="s">
         <v>52</v>
       </c>
